--- a/Validated_Part.xlsx
+++ b/Validated_Part.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM-8\Track1\final-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C425875-F713-4E33-8D87-387F25E6610F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DB6875-13BF-4DF0-9E6B-E917E7818121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -7397,6 +7397,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7414,9 +7417,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7732,18 +7732,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>2356</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21"/>
+      <c r="A2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -7851,28 +7851,28 @@
       <c r="G7" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>2373</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="5">
         <v>153200</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>2374</v>
       </c>
-      <c r="B10" s="14"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="5">
         <v>2478</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>2375</v>
       </c>
-      <c r="B11" s="14"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="5">
         <v>150722</v>
       </c>
@@ -7899,11 +7899,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>2379</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
@@ -7917,10 +7917,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="16">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -7928,24 +7928,24 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="12" t="s">
         <v>2383</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
       <c r="C6" s="12" t="s">
         <v>2384</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="16">
+      <c r="A7" s="17">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -7953,8 +7953,8 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
       <c r="C8" s="12" t="s">
         <v>2385</v>
       </c>
@@ -7971,10 +7971,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="16">
+      <c r="A10" s="17">
         <v>4</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -7982,8 +7982,8 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
       <c r="C11" s="12" t="s">
         <v>2386</v>
       </c>
@@ -8000,10 +8000,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="16">
+      <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -8011,8 +8011,8 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="12" t="s">
         <v>2387</v>
       </c>
@@ -8029,10 +8029,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="16">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -8040,17 +8040,17 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="12" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="16">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -8058,17 +8058,17 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
       <c r="C19" s="12" t="s">
         <v>2390</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="16">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -8076,8 +8076,8 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="12" t="s">
         <v>2390</v>
       </c>
